--- a/cpi_migrator/output/gap_analysis.xlsx
+++ b/cpi_migrator/output/gap_analysis.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAP S-4HANA Cloud (Public Editi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interface Inventory'!$A$1:$N$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SAP S-4HANA Cloud (Public Editi'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interface Inventory'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SAP S-4HANA Cloud (Public Editi'!$A$1:$I$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,13 +119,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-04 23:12</t>
+          <t>Generated: 2026-06-09 21:25</t>
         </is>
       </c>
     </row>
@@ -537,7 +540,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -547,7 +550,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +560,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +570,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -578,7 +581,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11.0 days</t>
+          <t>134.9 days</t>
         </is>
       </c>
     </row>
@@ -609,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -703,27 +706,23 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>PO_to_S4_Create</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>http://company.com/po</t>
-        </is>
-      </c>
+          <t>Employee Services - Terminate</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr"/>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>Sender</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>IDoc</t>
+          <t>SOAP</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>S4HANA</t>
+          <t>Receiver1</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
@@ -741,62 +740,54 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>MM_PO_Create</t>
-        </is>
-      </c>
+      <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="K2" s="8" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>3</v>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>IDoc Receiver / Sender Adapter</t>
+          <t>Point-to-Point HTTP/SOAP</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>IDoc requires SAP system partner profile setup in CPI.</t>
+          <t>8 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 3 mapping(s), 0 script(s), 1 receiver(s)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Employee_Sync</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>http://company.com/hr</t>
-        </is>
-      </c>
+          <t>OAUTH Token Revoke</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr"/>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>S4HANA</t>
+          <t>Sender</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>RFC</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>SuccessFactors</t>
+          <t>Receiver1</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -809,62 +800,54 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>MM_EmpSync</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="8" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>RFC → SOAP/OData Bridge</t>
+          <t>Point-to-Point HTTP/SOAP</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>RFC → OData/SOAP conversion needed; BAPI calls require CPI RFC adapter or wrapping.</t>
+          <t>13 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 2 mapping(s), 4 script(s), 1 receiver(s)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Ariba_PO_Out</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>http://company.com/ariba</t>
-        </is>
-      </c>
+          <t>OAUTH Token</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr"/>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>Sender</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>File</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Ariba</t>
+          <t>Receiver1</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -878,53 +861,53 @@
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="K4" s="8" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>File Sender → Service Call</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr"/>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>9 steps, 0 local process(es), 0 route(s), 0 exception subprocess(es), 1 mapping(s), 2 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>IDoc_Inbound</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>http://company.com/idoc</t>
-        </is>
-      </c>
+          <t>Employee Services - Create</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr"/>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>Sender</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>IDoc</t>
+          <t>SOAP</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>S4HANA</t>
+          <t>Receiver1</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>IDoc</t>
+          <t>SOAP</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -938,42 +921,38 @@
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="K5" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>IDoc Receiver / Sender Adapter</t>
+          <t>Point-to-Point HTTP/SOAP</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>IDoc requires SAP system partner profile setup in CPI.</t>
+          <t>7 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 2 mapping(s), 0 script(s), 1 receiver(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>BPM_Invoice</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>http://company.com/inv</t>
-        </is>
-      </c>
+          <t>Employment Information - Pay Date File</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr"/>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>Sender</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -983,12 +962,12 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>S4HANA</t>
+          <t>Receiver1</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>RFC</t>
+          <t>SOAP</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1001,35 +980,798 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>MM_Invoice</t>
-        </is>
-      </c>
+      <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
       <c r="K6" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>3</v>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>RFC → SOAP/OData Bridge</t>
+          <t>Point-to-Point HTTP/SOAP</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>RFC → OData/SOAP conversion needed; BAPI calls require CPI RFC adapter or wrapping.</t>
+          <t>7 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 2 mapping(s), 0 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>OAUTH Token Validation</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>13 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 2 mapping(s), 4 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>OAUTH Token Validation Backend</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Receiver1</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>11 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 0 mapping(s), 3 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Employee Services - Update</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Receiver1</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>7 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 2 mapping(s), 0 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>OAUTH Token Validation V2</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>17 steps, 0 local process(es), 2 route(s), 1 exception subprocess(es), 2 mapping(s), 5 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>OAUTH Token Revoke V2</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>17 steps, 0 local process(es), 2 route(s), 1 exception subprocess(es), 2 mapping(s), 5 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Employee Services - Terminate V2</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>11 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 0 mapping(s), 0 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Employee Services - Create V2</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>11 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 0 mapping(s), 0 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>OAUTH Token Validation Backend V2</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>15 steps, 0 local process(es), 2 route(s), 1 exception subprocess(es), 0 mapping(s), 3 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>OAUTH Token V2</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>10 steps, 0 local process(es), 0 route(s), 0 exception subprocess(es), 1 mapping(s), 2 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Employment Information - Pay Date File V2</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>11 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 0 mapping(s), 0 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Employee Services - Update V2</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Sender</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>11 steps, 0 local process(es), 0 route(s), 1 exception subprocess(es), 0 mapping(s), 0 script(s), 1 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>RCI093_Clear_CustomFields</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr"/>
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>Unknown sender adapter '' — manual review needed.
+Unknown receiver adapter 'SuccessFactors' — manual review needed.
+5 steps, 0 local process(es), 0 route(s), 0 exception subprocess(es), 0 mapping(s), 2 script(s), 3 receiver(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>RCI093_SuccessFactors_to_OpenText_SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr"/>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Send_Mail_CompletedRun</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>Point-to-Point HTTP/SOAP</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>Unknown sender adapter '' — manual review needed.
+54 steps, 3 local process(es), 12 route(s), 3 exception subprocess(es), 7 mapping(s), 9 script(s), 14 receiver(s)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N6"/>
+  <autoFilter ref="A1:N19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1040,7 +1782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1846,12 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PO_to_S4_Create</t>
+          <t>Employee Services - Terminate</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>IDoc → IDoc</t>
+          <t>SOAP → SOAP</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -1129,13 +1871,12 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>×1.5</t>
+          <t>×1.0</t>
         </is>
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>[IntegrationFlow] Invoice Processing S4HANA Cloud
-[IntegrationFlow] Goods Receipt Notification S4HANA Cloud
+          <t>[IntegrationFlow] Employee Master Data Replication
 [IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
         </is>
       </c>
@@ -1156,17 +1897,17 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Employee_Sync</t>
+          <t>OAUTH Token Revoke</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>RFC → OData</t>
+          <t>HTTPS → HTTPS</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>HTTPS → HTTPS</t>
+          <t>HTTP → HTTPS</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -1181,13 +1922,12 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>×1.5</t>
+          <t>×1.0</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>[IntegrationFlow] Employee Master Data Replication
-[IntegrationFlow] Material Master Replication S4HANA Cloud</t>
+          <t>None found</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
@@ -1207,17 +1947,17 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Ariba_PO_Out</t>
+          <t>OAUTH Token</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>File → HTTPS</t>
+          <t>HTTPS → HTTPS</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>HTTPS → HTTPS</t>
+          <t>HTTP → HTTPS</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -1257,17 +1997,17 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>IDoc_Inbound</t>
+          <t>Employee Services - Create</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>IDoc → IDoc</t>
+          <t>SOAP → SOAP</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>IDoc → IDoc</t>
+          <t>SOAP → SOAP</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -1282,13 +2022,12 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>×1.5</t>
+          <t>×1.0</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>[IntegrationFlow] Invoice Processing S4HANA Cloud
-[IntegrationFlow] Goods Receipt Notification S4HANA Cloud
+          <t>[IntegrationFlow] Employee Master Data Replication
 [IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
         </is>
       </c>
@@ -1309,7 +2048,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>BPM_Invoice</t>
+          <t>Employment Information - Pay Date File</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1319,7 +2058,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>RFC → OData</t>
+          <t>SOAP → SOAP</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -1339,8 +2078,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>[IntegrationFlow] Invoice Processing S4HANA Cloud
-[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
+          <t>[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1357,8 +2095,672 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>OAUTH Token Validation</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>HTTPS → HTTPS</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>HTTP → HTTPS</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>OAUTH Token Validation Backend</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>HTTP → HTTPS</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Employee Services - Update</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Employee Master Data Replication
+[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>OAUTH Token Validation V2</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>HTTPS → HTTPS</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>HTTP → HTTPS</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>OAUTH Token Revoke V2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>HTTPS → HTTPS</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>HTTP → HTTPS</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Employee Services - Terminate V2</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Employee Master Data Replication
+[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Employee Services - Create V2</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Employee Master Data Replication
+[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>OAUTH Token Validation Backend V2</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>HTTP → HTTPS</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>OAUTH Token V2</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>HTTPS → HTTPS</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>HTTP → HTTPS</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Employment Information - Pay Date File V2</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Employee Services - Update V2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>SOAP → SOAP</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Employee Master Data Replication
+[IntegrationFlow] Payment Advice Processing S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>RCI093_Clear_CustomFields</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> → </t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>SuccessFactors → SuccessFactors</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>⚠ No</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Purchase Order Replication to S4HANA Cloud
+[IntegrationFlow] Sales Order Integration S4HANA Cloud
+[IntegrationFlow] Invoice Processing S4HANA Cloud
+[IntegrationFlow] Employee Master Data Replication
+[IntegrationFlow] Material Master Replication S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Sender adapter '' not officially supported by SAP S/4HANA Cloud (Public Edition).
+Receiver adapter 'SuccessFactors' not officially supported by SAP S/4HANA Cloud (Public Edition).</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>RCI093_SuccessFactors_to_OpenText_SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> → </t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Mail → Mail</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>⚠ No</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>[IntegrationFlow] Purchase Order Replication to S4HANA Cloud
+[IntegrationFlow] Sales Order Integration S4HANA Cloud
+[IntegrationFlow] Invoice Processing S4HANA Cloud
+[IntegrationFlow] Employee Master Data Replication
+[IntegrationFlow] Material Master Replication S4HANA Cloud</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Sender adapter '' not officially supported by SAP S/4HANA Cloud (Public Edition).
+Receiver adapter 'Mail' not officially supported by SAP S/4HANA Cloud (Public Edition).</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>S/4HANA Cloud enforces Clean Core — all integrations must use published APIs (Tier-1).
+Custom RFC/BAPI calls are not supported; map to equivalent OData V4 API on the Hub.
+IDoc over HTTPS (IDoc adapter) is supported; configure communication arrangement in S/4.
+Check SAP Note 3085212 for the current supported API list before scaffolding.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:I19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>